--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -1144,7 +1144,7 @@
     <t>0.0007,0.9996,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.1033,0.9628,0.0006,0.0000</t>
+    <t>0.1033,0.9627,0.0006,0.0000</t>
   </si>
   <si>
     <t>0.0731,0.9649,0.0019,0.0000</t>
@@ -1216,7 +1216,7 @@
     <t>0.0053,0.9629,0.3535,0.0017</t>
   </si>
   <si>
-    <t>0.0021,0.1890,0.9938,0.0001</t>
+    <t>0.0021,0.1891,0.9938,0.0001</t>
   </si>
   <si>
     <t>0.0009,0.0040,0.9986,0.0002</t>
@@ -1282,7 +1282,7 @@
     <t>0.9784,0.0565,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.6818,0.6412,0.0005,0.0000</t>
+    <t>0.6819,0.6412,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.9882,0.0158,0.0016,0.0000</t>
@@ -1441,7 +1441,7 @@
     <t>0.0147,0.0044,0.9895,0.0003</t>
   </si>
   <si>
-    <t>0.2020,0.0462,0.6011,0.0006</t>
+    <t>0.2020,0.0462,0.6010,0.0006</t>
   </si>
   <si>
     <t>0.9974,0.0066,0.0001,0.0000</t>
@@ -1468,7 +1468,7 @@
     <t>0.9965,0.0098,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.4702,0.0215,0.5057,0.0001</t>
+    <t>0.4703,0.0215,0.5057,0.0001</t>
   </si>
   <si>
     <t>0.6407,0.1695,0.0547,0.0001</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -817,19 +817,25 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9849,0.0091,0.0040,0.0002</t>
   </si>
   <si>
-    <t>0.8357,0.1099,0.0031,0.0117</t>
-  </si>
-  <si>
-    <t>0.9904,0.0147,0.0013,0.0001</t>
+    <t>0.8362,0.1096,0.0031,0.0116</t>
+  </si>
+  <si>
+    <t>0.9904,0.0146,0.0013,0.0001</t>
   </si>
   <si>
     <t>0.9812,0.0229,0.0012,0.0005</t>
@@ -847,7 +853,7 @@
     <t>0.9983,0.0065,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9922,0.0382,0.0001,0.0000</t>
+    <t>0.9922,0.0381,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9898,0.0168,0.0007,0.0000</t>
@@ -859,22 +865,22 @@
     <t>0.9936,0.0078,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.9146,0.0525,0.0214,0.0003</t>
-  </si>
-  <si>
-    <t>0.1581,0.1971,0.6458,0.0006</t>
-  </si>
-  <si>
-    <t>0.4891,0.0027,0.6797,0.0000</t>
-  </si>
-  <si>
-    <t>0.0897,0.0109,0.9520,0.0002</t>
+    <t>0.9147,0.0525,0.0214,0.0003</t>
+  </si>
+  <si>
+    <t>0.1584,0.1967,0.6456,0.0006</t>
+  </si>
+  <si>
+    <t>0.4896,0.0027,0.6793,0.0000</t>
+  </si>
+  <si>
+    <t>0.0898,0.0109,0.9519,0.0002</t>
   </si>
   <si>
     <t>0.9720,0.0107,0.0114,0.0001</t>
   </si>
   <si>
-    <t>0.0026,0.9986,0.0003,0.0000</t>
+    <t>0.0027,0.9986,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.0188,0.9931,0.0003,0.0000</t>
@@ -883,70 +889,70 @@
     <t>0.0156,0.9942,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0322,0.9898,0.0002,0.0000</t>
+    <t>0.0323,0.9898,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.9997,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6325,0.0195,0.3708,0.0003</t>
-  </si>
-  <si>
-    <t>0.2521,0.0523,0.7462,0.0006</t>
-  </si>
-  <si>
-    <t>0.1822,0.0020,0.9226,0.0000</t>
-  </si>
-  <si>
-    <t>0.1007,0.0214,0.9374,0.0003</t>
-  </si>
-  <si>
-    <t>0.3406,0.0463,0.6373,0.0003</t>
-  </si>
-  <si>
-    <t>0.0678,0.0013,0.9691,0.0001</t>
+    <t>0.6327,0.0195,0.3707,0.0003</t>
+  </si>
+  <si>
+    <t>0.2523,0.0522,0.7461,0.0006</t>
+  </si>
+  <si>
+    <t>0.1824,0.0020,0.9225,0.0000</t>
+  </si>
+  <si>
+    <t>0.1007,0.0213,0.9374,0.0003</t>
+  </si>
+  <si>
+    <t>0.3408,0.0462,0.6374,0.0003</t>
+  </si>
+  <si>
+    <t>0.0679,0.0013,0.9691,0.0001</t>
   </si>
   <si>
     <t>0.0083,0.0003,0.9956,0.0000</t>
   </si>
   <si>
-    <t>0.8452,0.2894,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.8555,0.3459,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.1504,0.0233,0.8720,0.0003</t>
-  </si>
-  <si>
-    <t>0.1344,0.7960,0.0799,0.0005</t>
-  </si>
-  <si>
-    <t>0.9597,0.1138,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9593,0.1045,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.6337,0.6493,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.1055,0.9568,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.9832,0.1056,0.0017</t>
+    <t>0.8455,0.2889,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.8557,0.3455,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.1505,0.0233,0.8720,0.0003</t>
+  </si>
+  <si>
+    <t>0.1346,0.7954,0.0800,0.0005</t>
+  </si>
+  <si>
+    <t>0.9598,0.1136,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9593,0.1042,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.6342,0.6487,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.1057,0.9567,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9831,0.1059,0.0017</t>
   </si>
   <si>
     <t>0.0060,0.0006,0.9930,0.0007</t>
   </si>
   <si>
-    <t>0.0439,0.0254,0.9568,0.0019</t>
-  </si>
-  <si>
-    <t>0.8089,0.0062,0.1490,0.0030</t>
-  </si>
-  <si>
-    <t>0.0029,0.9718,0.2494,0.0025</t>
+    <t>0.0439,0.0253,0.9568,0.0019</t>
+  </si>
+  <si>
+    <t>0.8092,0.0062,0.1487,0.0030</t>
+  </si>
+  <si>
+    <t>0.0029,0.9718,0.2497,0.0025</t>
   </si>
   <si>
     <t>0.0016,0.9921,0.0245,0.0026</t>
@@ -955,7 +961,7 @@
     <t>0.0052,0.0030,0.9961,0.0001</t>
   </si>
   <si>
-    <t>0.3089,0.7291,0.0067,0.0028</t>
+    <t>0.3096,0.7286,0.0067,0.0028</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
@@ -964,16 +970,16 @@
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0029,0.0278,0.9939,0.0003</t>
-  </si>
-  <si>
-    <t>0.0092,0.0255,0.9849,0.0008</t>
-  </si>
-  <si>
-    <t>0.0273,0.0045,0.9843,0.0002</t>
-  </si>
-  <si>
-    <t>0.3095,0.0076,0.7887,0.0001</t>
+    <t>0.0029,0.0277,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0255,0.9850,0.0008</t>
+  </si>
+  <si>
+    <t>0.0273,0.0045,0.9842,0.0002</t>
+  </si>
+  <si>
+    <t>0.3097,0.0076,0.7887,0.0001</t>
   </si>
   <si>
     <t>0.0139,0.0021,0.9934,0.0000</t>
@@ -982,19 +988,19 @@
     <t>0.0407,0.0160,0.9753,0.0003</t>
   </si>
   <si>
-    <t>0.9808,0.0407,0.0007,0.0000</t>
+    <t>0.9808,0.0406,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.9944,0.0098,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.9879,0.0134,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9711,0.0163,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0078,0.0005,0.0000</t>
+    <t>0.9880,0.0134,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.9712,0.0162,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0077,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.9956,0.0053,0.0006,0.0000</t>
@@ -1003,16 +1009,16 @@
     <t>0.9960,0.0090,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9950,0.8291,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0032,0.9993,0.0000</t>
+    <t>0.0002,0.9950,0.8292,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0032,0.9993,0.0000</t>
   </si>
   <si>
     <t>0.0023,0.0026,0.9982,0.0000</t>
   </si>
   <si>
-    <t>0.0012,0.8946,0.9700,0.0002</t>
+    <t>0.0012,0.8945,0.9700,0.0002</t>
   </si>
   <si>
     <t>0.0007,0.0001,0.9987,0.0002</t>
@@ -1021,76 +1027,76 @@
     <t>0.0017,0.9992,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9830,0.0104,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.8265,0.1341,0.0293,0.0005</t>
-  </si>
-  <si>
-    <t>0.2321,0.0240,0.8021,0.0002</t>
-  </si>
-  <si>
-    <t>0.0016,0.8272,0.9736,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.8680,0.9646,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0117,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9959,0.2527,0.0009</t>
-  </si>
-  <si>
-    <t>0.9002,0.0926,0.0098,0.0075</t>
-  </si>
-  <si>
-    <t>0.6462,0.1384,0.0013,0.0747</t>
-  </si>
-  <si>
-    <t>0.8363,0.0393,0.0037,0.0437</t>
-  </si>
-  <si>
-    <t>0.9708,0.0253,0.0016,0.0028</t>
-  </si>
-  <si>
-    <t>0.9630,0.0400,0.0033,0.0017</t>
-  </si>
-  <si>
-    <t>0.5683,0.1811,0.0066,0.1266</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.1202,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.1861,0.9928,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.9214,0.5000,0.0017</t>
-  </si>
-  <si>
-    <t>0.0041,0.7295,0.9383,0.0007</t>
+    <t>0.9831,0.0104,0.0044,0.0000</t>
+  </si>
+  <si>
+    <t>0.8267,0.1339,0.0293,0.0005</t>
+  </si>
+  <si>
+    <t>0.2323,0.0240,0.8019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.8271,0.9736,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.8679,0.9646,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0118,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9959,0.2528,0.0009</t>
+  </si>
+  <si>
+    <t>0.9003,0.0924,0.0098,0.0074</t>
+  </si>
+  <si>
+    <t>0.6469,0.1382,0.0013,0.0745</t>
+  </si>
+  <si>
+    <t>0.8368,0.0393,0.0037,0.0435</t>
+  </si>
+  <si>
+    <t>0.9709,0.0252,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.9631,0.0399,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.5691,0.1807,0.0066,0.1262</t>
+  </si>
+  <si>
+    <t>0.0004,0.9987,0.1204,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.1858,0.9928,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9213,0.5004,0.0016</t>
+  </si>
+  <si>
+    <t>0.0041,0.7290,0.9384,0.0007</t>
   </si>
   <si>
     <t>0.0003,0.9824,0.9598,0.0001</t>
   </si>
   <si>
-    <t>0.0007,0.9975,0.0274,0.0008</t>
+    <t>0.0007,0.9975,0.0275,0.0008</t>
   </si>
   <si>
     <t>0.9956,0.0094,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9745,0.0374,0.0013,0.0000</t>
+    <t>0.9745,0.0373,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9967,0.0156,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9928,0.0126,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9905,0.0225,0.0004,0.0000</t>
+    <t>0.9928,0.0125,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9905,0.0224,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.9994,0.0010,0.0000,0.0000</t>
@@ -1129,13 +1135,13 @@
     <t>0.0039,0.0003,0.9983,0.0000</t>
   </si>
   <si>
-    <t>0.6270,0.0385,0.2893,0.0003</t>
+    <t>0.6271,0.0384,0.2894,0.0003</t>
   </si>
   <si>
     <t>0.9127,0.0027,0.1012,0.0000</t>
   </si>
   <si>
-    <t>0.3081,0.0182,0.7305,0.0001</t>
+    <t>0.3082,0.0181,0.7305,0.0001</t>
   </si>
   <si>
     <t>0.0010,0.9996,0.0000,0.0000</t>
@@ -1144,10 +1150,10 @@
     <t>0.0007,0.9996,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.1033,0.9627,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0731,0.9649,0.0019,0.0000</t>
+    <t>0.1034,0.9627,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0732,0.9648,0.0019,0.0000</t>
   </si>
   <si>
     <t>0.0005,0.9998,0.0000,0.0000</t>
@@ -1156,22 +1162,22 @@
     <t>0.0002,0.9999,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7460,0.4256,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.5401,0.2456,0.0877,0.0005</t>
-  </si>
-  <si>
-    <t>0.1478,0.0099,0.9114,0.0003</t>
-  </si>
-  <si>
-    <t>0.6026,0.1234,0.1818,0.0008</t>
-  </si>
-  <si>
-    <t>0.5052,0.0788,0.3413,0.0006</t>
-  </si>
-  <si>
-    <t>0.0156,0.9634,0.0364,0.0287</t>
+    <t>0.7464,0.4250,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.5404,0.2452,0.0879,0.0005</t>
+  </si>
+  <si>
+    <t>0.1479,0.0099,0.9114,0.0003</t>
+  </si>
+  <si>
+    <t>0.6030,0.1232,0.1818,0.0008</t>
+  </si>
+  <si>
+    <t>0.5053,0.0787,0.3415,0.0006</t>
+  </si>
+  <si>
+    <t>0.0156,0.9633,0.0364,0.0287</t>
   </si>
   <si>
     <t>0.0008,0.9991,0.0002,0.0001</t>
@@ -1183,10 +1189,10 @@
     <t>0.0052,0.9975,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.6879,0.5835,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.6049,0.6827,0.0010,0.0000</t>
+    <t>0.6884,0.5828,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.6056,0.6821,0.0010,0.0000</t>
   </si>
   <si>
     <t>0.9974,0.0052,0.0002,0.0000</t>
@@ -1204,19 +1210,19 @@
     <t>0.9994,0.0012,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9939,0.0111,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0051,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0040,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0053,0.9629,0.3535,0.0017</t>
-  </si>
-  <si>
-    <t>0.0021,0.1891,0.9938,0.0001</t>
+    <t>0.9939,0.0110,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0050,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9966,0.0039,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.9629,0.3537,0.0017</t>
+  </si>
+  <si>
+    <t>0.0021,0.1888,0.9938,0.0001</t>
   </si>
   <si>
     <t>0.0009,0.0040,0.9986,0.0002</t>
@@ -1228,43 +1234,43 @@
     <t>0.9664,0.0135,0.0144,0.0001</t>
   </si>
   <si>
-    <t>0.6138,0.3743,0.0193,0.0004</t>
-  </si>
-  <si>
-    <t>0.0777,0.0003,0.9669,0.0000</t>
-  </si>
-  <si>
-    <t>0.7927,0.0851,0.0685,0.0004</t>
+    <t>0.6144,0.3736,0.0193,0.0004</t>
+  </si>
+  <si>
+    <t>0.0779,0.0003,0.9668,0.0000</t>
+  </si>
+  <si>
+    <t>0.7929,0.0849,0.0685,0.0004</t>
   </si>
   <si>
     <t>0.9914,0.0085,0.0014,0.0005</t>
   </si>
   <si>
-    <t>0.0032,0.2540,0.0002,0.9955</t>
-  </si>
-  <si>
-    <t>0.0589,0.0803,0.0010,0.9473</t>
-  </si>
-  <si>
-    <t>0.9634,0.0329,0.0020,0.0031</t>
-  </si>
-  <si>
-    <t>0.0011,0.9805,0.7197,0.0009</t>
+    <t>0.0032,0.2537,0.0002,0.9955</t>
+  </si>
+  <si>
+    <t>0.0591,0.0802,0.0010,0.9472</t>
+  </si>
+  <si>
+    <t>0.9635,0.0328,0.0020,0.0031</t>
+  </si>
+  <si>
+    <t>0.0011,0.9805,0.7196,0.0009</t>
   </si>
   <si>
     <t>0.9958,0.0080,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.4027,0.8156,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0068,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.6302,0.6585,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9936,0.0066,0.0013,0.0000</t>
+    <t>0.4032,0.8153,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0067,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6307,0.6579,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9936,0.0065,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9903,0.0001,0.0065,0.0000</t>
@@ -1279,22 +1285,22 @@
     <t>0.9978,0.0022,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9784,0.0565,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.6819,0.6412,0.0005,0.0000</t>
+    <t>0.9784,0.0563,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6823,0.6406,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.9882,0.0158,0.0016,0.0000</t>
   </si>
   <si>
-    <t>0.9516,0.0822,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.3617,0.7103,0.0122,0.0002</t>
-  </si>
-  <si>
-    <t>0.9576,0.0428,0.0050,0.0001</t>
+    <t>0.9517,0.0820,0.0026,0.0001</t>
+  </si>
+  <si>
+    <t>0.3623,0.7097,0.0122,0.0002</t>
+  </si>
+  <si>
+    <t>0.9577,0.0427,0.0050,0.0001</t>
   </si>
   <si>
     <t>0.9761,0.0269,0.0042,0.0001</t>
@@ -1306,40 +1312,40 @@
     <t>0.9976,0.0105,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9815,0.0090,0.0039,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0074,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9830,0.0113,0.0024,0.0000</t>
+    <t>0.9816,0.0090,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0073,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9830,0.0112,0.0024,0.0000</t>
   </si>
   <si>
     <t>0.9858,0.0121,0.0019,0.0000</t>
   </si>
   <si>
-    <t>0.9891,0.0100,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0070,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7553,0.5106,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.7336,0.3695,0.0051,0.0001</t>
-  </si>
-  <si>
-    <t>0.9429,0.1992,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9149,0.0415,0.0121,0.0000</t>
+    <t>0.9892,0.0100,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0069,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7555,0.5102,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.7340,0.3688,0.0051,0.0001</t>
+  </si>
+  <si>
+    <t>0.9430,0.1988,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9150,0.0414,0.0121,0.0000</t>
   </si>
   <si>
     <t>0.9955,0.0151,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9364,0.0973,0.0028,0.0000</t>
+    <t>0.9365,0.0971,0.0028,0.0000</t>
   </si>
   <si>
     <t>0.9942,0.0143,0.0003,0.0000</t>
@@ -1348,25 +1354,25 @@
     <t>0.9793,0.0259,0.0018,0.0000</t>
   </si>
   <si>
-    <t>0.1451,0.0279,0.8559,0.0000</t>
-  </si>
-  <si>
-    <t>0.9702,0.0463,0.0016,0.0000</t>
+    <t>0.1453,0.0278,0.8558,0.0000</t>
+  </si>
+  <si>
+    <t>0.9703,0.0462,0.0016,0.0000</t>
   </si>
   <si>
     <t>0.0039,0.0009,0.9979,0.0000</t>
   </si>
   <si>
-    <t>0.0064,0.1483,0.9544,0.0021</t>
-  </si>
-  <si>
-    <t>0.4252,0.1640,0.2902,0.0015</t>
-  </si>
-  <si>
-    <t>0.0174,0.4039,0.8896,0.0004</t>
-  </si>
-  <si>
-    <t>0.0359,0.0827,0.9615,0.0003</t>
+    <t>0.0065,0.1481,0.9545,0.0021</t>
+  </si>
+  <si>
+    <t>0.4256,0.1637,0.2902,0.0015</t>
+  </si>
+  <si>
+    <t>0.0174,0.4034,0.8897,0.0004</t>
+  </si>
+  <si>
+    <t>0.0359,0.0825,0.9615,0.0003</t>
   </si>
   <si>
     <t>0.0082,0.0002,0.9972,0.0000</t>
@@ -1375,106 +1381,106 @@
     <t>0.0465,0.0054,0.9767,0.0001</t>
   </si>
   <si>
-    <t>0.1995,0.0422,0.8173,0.0005</t>
-  </si>
-  <si>
-    <t>0.4691,0.0116,0.5948,0.0003</t>
-  </si>
-  <si>
-    <t>0.5326,0.2523,0.1056,0.0007</t>
-  </si>
-  <si>
-    <t>0.2158,0.0947,0.7159,0.0006</t>
-  </si>
-  <si>
-    <t>0.1688,0.3242,0.4280,0.0004</t>
-  </si>
-  <si>
-    <t>0.3185,0.0098,0.7731,0.0004</t>
-  </si>
-  <si>
-    <t>0.6421,0.0643,0.2262,0.0004</t>
-  </si>
-  <si>
-    <t>0.4279,0.1026,0.4168,0.0006</t>
-  </si>
-  <si>
-    <t>0.2261,0.9311,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4335,0.7819,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.7511,0.4376,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.9883,0.0360,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9481,0.1293,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.3019,0.7702,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.9642,0.0214,0.0122,0.0002</t>
-  </si>
-  <si>
-    <t>0.6212,0.1043,0.2173,0.0011</t>
-  </si>
-  <si>
-    <t>0.4041,0.0028,0.7483,0.0003</t>
-  </si>
-  <si>
-    <t>0.9350,0.0353,0.0193,0.0003</t>
+    <t>0.1996,0.0421,0.8174,0.0005</t>
+  </si>
+  <si>
+    <t>0.4692,0.0115,0.5948,0.0003</t>
+  </si>
+  <si>
+    <t>0.5330,0.2518,0.1057,0.0007</t>
+  </si>
+  <si>
+    <t>0.2159,0.0946,0.7159,0.0006</t>
+  </si>
+  <si>
+    <t>0.1691,0.3235,0.4282,0.0004</t>
+  </si>
+  <si>
+    <t>0.3189,0.0098,0.7728,0.0004</t>
+  </si>
+  <si>
+    <t>0.6425,0.0641,0.2260,0.0004</t>
+  </si>
+  <si>
+    <t>0.4282,0.1025,0.4165,0.0006</t>
+  </si>
+  <si>
+    <t>0.2265,0.9309,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4341,0.7815,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.7516,0.4369,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.9884,0.0359,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9483,0.1290,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.3023,0.7698,0.0094,0.0002</t>
+  </si>
+  <si>
+    <t>0.9642,0.0213,0.0122,0.0002</t>
+  </si>
+  <si>
+    <t>0.6212,0.1042,0.2175,0.0011</t>
+  </si>
+  <si>
+    <t>0.4043,0.0028,0.7482,0.0003</t>
+  </si>
+  <si>
+    <t>0.9351,0.0352,0.0193,0.0003</t>
   </si>
   <si>
     <t>0.0529,0.0084,0.9698,0.0002</t>
   </si>
   <si>
-    <t>0.3528,0.0731,0.3938,0.0083</t>
-  </si>
-  <si>
-    <t>0.4748,0.1281,0.2009,0.0027</t>
+    <t>0.3527,0.0730,0.3942,0.0083</t>
+  </si>
+  <si>
+    <t>0.4753,0.1278,0.2009,0.0027</t>
   </si>
   <si>
     <t>0.0147,0.0044,0.9895,0.0003</t>
   </si>
   <si>
-    <t>0.2020,0.0462,0.6010,0.0006</t>
+    <t>0.2022,0.0461,0.6012,0.0006</t>
   </si>
   <si>
     <t>0.9974,0.0066,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9792,0.0246,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9645,0.0590,0.0017,0.0000</t>
+    <t>0.9792,0.0245,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9645,0.0589,0.0017,0.0000</t>
   </si>
   <si>
     <t>0.9965,0.0159,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9807,0.0266,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.9841,0.0222,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.9769,0.0260,0.0020,0.0000</t>
+    <t>0.9807,0.0265,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9842,0.0221,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9769,0.0259,0.0020,0.0000</t>
   </si>
   <si>
     <t>0.9965,0.0098,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.4703,0.0215,0.5057,0.0001</t>
-  </si>
-  <si>
-    <t>0.6407,0.1695,0.0547,0.0001</t>
-  </si>
-  <si>
-    <t>0.8114,0.0315,0.1074,0.0003</t>
+    <t>0.4707,0.0214,0.5054,0.0001</t>
+  </si>
+  <si>
+    <t>0.6411,0.1691,0.0547,0.0001</t>
+  </si>
+  <si>
+    <t>0.8116,0.0315,0.1074,0.0003</t>
   </si>
   <si>
     <t>0.0007,0.0001,0.9996,0.0000</t>
@@ -1495,34 +1501,34 @@
     <t>0.0032,0.0019,0.9982,0.0000</t>
   </si>
   <si>
-    <t>0.2198,0.2004,0.6030,0.0017</t>
-  </si>
-  <si>
-    <t>0.8367,0.0081,0.1565,0.0003</t>
-  </si>
-  <si>
-    <t>0.8667,0.0092,0.1238,0.0004</t>
-  </si>
-  <si>
-    <t>0.9579,0.0255,0.0123,0.0002</t>
+    <t>0.2200,0.2002,0.6028,0.0017</t>
+  </si>
+  <si>
+    <t>0.8368,0.0080,0.1564,0.0003</t>
+  </si>
+  <si>
+    <t>0.8669,0.0091,0.1237,0.0004</t>
+  </si>
+  <si>
+    <t>0.9579,0.0254,0.0123,0.0002</t>
   </si>
   <si>
     <t>0.9962,0.0127,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9945,0.0246,0.0001,0.0000</t>
+    <t>0.9945,0.0245,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9885,0.0213,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.9210,0.1218,0.0023,0.0000</t>
+    <t>0.9212,0.1215,0.0023,0.0000</t>
   </si>
   <si>
     <t>0.9982,0.0049,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9746,0.0534,0.0009,0.0000</t>
+    <t>0.9747,0.0533,0.0009,0.0000</t>
   </si>
   <si>
     <t>0.9934,0.0097,0.0006,0.0000</t>
@@ -1531,7 +1537,7 @@
     <t>0.9799,0.0214,0.0021,0.0000</t>
   </si>
   <si>
-    <t>0.0218,0.1490,0.9613,0.0005</t>
+    <t>0.0219,0.1488,0.9614,0.0005</t>
   </si>
   <si>
     <t>0.0083,0.0083,0.9954,0.0001</t>
@@ -1540,37 +1546,37 @@
     <t>0.0026,0.0022,0.9985,0.0000</t>
   </si>
   <si>
-    <t>0.0809,0.0574,0.9247,0.0006</t>
+    <t>0.0810,0.0573,0.9246,0.0006</t>
   </si>
   <si>
     <t>0.0267,0.0004,0.9895,0.0000</t>
   </si>
   <si>
-    <t>0.6724,0.4077,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.5129,0.4688,0.0327,0.0015</t>
+    <t>0.6729,0.4070,0.0009,0.0015</t>
+  </si>
+  <si>
+    <t>0.5134,0.4681,0.0327,0.0015</t>
   </si>
   <si>
     <t>0.0039,0.0002,0.9944,0.0006</t>
   </si>
   <si>
-    <t>0.9894,0.0076,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.3146,0.2736,0.0047,0.2976</t>
-  </si>
-  <si>
-    <t>0.9496,0.0329,0.0142,0.0035</t>
-  </si>
-  <si>
-    <t>0.0985,0.0049,0.0026,0.9578</t>
-  </si>
-  <si>
-    <t>0.3535,0.1073,0.0192,0.3541</t>
-  </si>
-  <si>
-    <t>0.9483,0.0399,0.0181,0.0017</t>
+    <t>0.9895,0.0076,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.3152,0.2732,0.0047,0.2970</t>
+  </si>
+  <si>
+    <t>0.9497,0.0329,0.0143,0.0035</t>
+  </si>
+  <si>
+    <t>0.0988,0.0049,0.0026,0.9577</t>
+  </si>
+  <si>
+    <t>0.3540,0.1071,0.0193,0.3534</t>
+  </si>
+  <si>
+    <t>0.9484,0.0399,0.0181,0.0017</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>265</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>266</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>265</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>265</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>265</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>265</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>265</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>265</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>266</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>266</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>265</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>266</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>265</v>
       </c>
       <c r="D50" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>265</v>
       </c>
       <c r="D51" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>265</v>
       </c>
       <c r="D52" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>265</v>
       </c>
       <c r="D53" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>265</v>
       </c>
       <c r="D54" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>265</v>
       </c>
       <c r="D55" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2813,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>265</v>
       </c>
       <c r="D64" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>265</v>
       </c>
       <c r="D65" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2855,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>265</v>
       </c>
       <c r="D67" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>266</v>
       </c>
       <c r="D68" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>266</v>
       </c>
       <c r="D69" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>265</v>
       </c>
       <c r="D72" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2953,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2967,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>266</v>
       </c>
       <c r="D75" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>264</v>
       </c>
       <c r="D82" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>266</v>
       </c>
       <c r="D83" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>265</v>
       </c>
       <c r="D84" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>266</v>
       </c>
       <c r="D88" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>265</v>
       </c>
       <c r="D105" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>266</v>
       </c>
       <c r="D109" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>266</v>
       </c>
       <c r="D114" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>266</v>
       </c>
       <c r="D121" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>266</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>266</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>266</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>265</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>265</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3961,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3975,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>264</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>265</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4398,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>265</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>265</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>265</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4521,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>265</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>265</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>265</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>265</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>265</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>265</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4871,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>265</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>265</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>265</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>265</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>265</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>265</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>265</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>265</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>265</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>265</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>265</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>265</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>265</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>265</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>265</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>265</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5459,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>264</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5487,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5501,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
